--- a/data/trans_orig/P36B06_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B06_R-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2007</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>361530</t>
+          <t>361973</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>397985</t>
+          <t>396896</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>243974</t>
+          <t>245843</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>270189</t>
+          <t>271045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>616539</t>
+          <t>617889</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>660208</t>
+          <t>660975</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,69%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>75791</t>
+          <t>76880</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>112246</t>
+          <t>111803</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>36491</t>
+          <t>35635</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62706</t>
+          <t>60837</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>120249</t>
+          <t>119482</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>163918</t>
+          <t>162568</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,83%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>272118</t>
+          <t>271129</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>303956</t>
+          <t>303236</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>273456</t>
+          <t>272511</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>304408</t>
+          <t>305453</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,54%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>554316</t>
+          <t>557075</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>599105</t>
+          <t>601383</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,5%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62096</t>
+          <t>62816</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>93934</t>
+          <t>94923</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>67457</t>
+          <t>66412</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>98409</t>
+          <t>99354</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>138812</t>
+          <t>136534</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>183601</t>
+          <t>180842</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>392714</t>
+          <t>394772</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>433054</t>
+          <t>435042</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,4%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>80,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>125400</t>
+          <t>124996</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>146089</t>
+          <t>146179</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,74%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>530224</t>
+          <t>527801</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>573781</t>
+          <t>573009</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,69%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>109335</t>
+          <t>107347</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>149675</t>
+          <t>147617</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21693</t>
+          <t>21603</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42382</t>
+          <t>42786</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>136390</t>
+          <t>137162</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>179947</t>
+          <t>182370</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,68%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>928001</t>
+          <t>924151</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>989408</t>
+          <t>987643</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>559588</t>
+          <t>559791</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>601116</t>
+          <t>602346</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1496718</t>
+          <t>1499078</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1573152</t>
+          <t>1572838</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,59%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>247978</t>
+          <t>249743</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>309385</t>
+          <t>313235</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>113169</t>
+          <t>111939</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>154697</t>
+          <t>154494</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>378520</t>
+          <t>378834</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>454954</t>
+          <t>452594</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>230865</t>
+          <t>228144</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>264047</t>
+          <t>263207</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>435008</t>
+          <t>434521</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>472025</t>
+          <t>472027</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>672397</t>
+          <t>676340</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>725452</t>
+          <t>726306</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,23%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>79,1%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86508</t>
+          <t>87348</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>119690</t>
+          <t>122411</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95667</t>
+          <t>95665</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>132684</t>
+          <t>133171</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>192795</t>
+          <t>191941</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>245850</t>
+          <t>241907</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>26,34%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>187005</t>
+          <t>185821</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>217377</t>
+          <t>217930</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,34%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1010301</t>
+          <t>1009531</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1059043</t>
+          <t>1062140</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>85,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1205494</t>
+          <t>1207097</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1267002</t>
+          <t>1269147</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,01%</t>
+          <t>82,15%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>79781</t>
+          <t>79228</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>110153</t>
+          <t>111337</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>188741</t>
+          <t>185644</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>237483</t>
+          <t>238253</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>277940</t>
+          <t>275795</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>339448</t>
+          <t>337845</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2439055</t>
+          <t>2438510</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2539462</t>
+          <t>2540339</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2711090</t>
+          <t>2714021</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2803628</t>
+          <t>2798435</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5175696</t>
+          <t>5176475</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5312330</t>
+          <t>5309890</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,96%</t>
+          <t>79,93%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>727856</t>
+          <t>726979</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>828263</t>
+          <t>828808</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>572461</t>
+          <t>577654</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>664999</t>
+          <t>662068</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1331076</t>
+          <t>1333516</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1467710</t>
+          <t>1466931</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2012</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>351925</t>
+          <t>353163</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>384050</t>
+          <t>384995</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>272369</t>
+          <t>273669</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>294659</t>
+          <t>294744</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>635480</t>
+          <t>633947</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>671428</t>
+          <t>673299</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,67%</t>
+          <t>84,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,7%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53161</t>
+          <t>52216</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>85286</t>
+          <t>84048</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18708</t>
+          <t>18623</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>40998</t>
+          <t>39698</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>79149</t>
+          <t>77278</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>115097</t>
+          <t>116630</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>340098</t>
+          <t>342684</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>371256</t>
+          <t>372129</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,82 +3725,82 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>81,41%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>89,08%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>292792</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>279583</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>304208</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>87,15%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>83,22%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>90,55%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>581</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>651012</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>630412</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>669858</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>86,37%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>83,64%</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
           <t>88,87%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>292792</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>279182</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>303743</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>87,15%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>83,1%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>90,41%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>581</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>651012</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>629290</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>670856</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>86,37%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>83,49%</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>89,01%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46500</t>
+          <t>45627</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77658</t>
+          <t>75072</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3838,82 +3838,82 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>10,92%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>17,97%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>43173</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>31757</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>56382</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>12,85%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>9,45%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>16,78%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>102709</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>83863</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>123309</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>13,63%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
           <t>11,13%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>18,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>43173</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>32222</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>56783</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>12,85%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>9,59%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>16,9%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>102709</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>82865</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>124431</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>13,63%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>10,99%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>497031</t>
+          <t>494662</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>535835</t>
+          <t>536455</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>211421</t>
+          <t>212347</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>234068</t>
+          <t>233905</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,12 +4103,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>714658</t>
+          <t>717948</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>763029</t>
+          <t>763561</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,78%</t>
+          <t>85,84%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>93580</t>
+          <t>92960</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>132384</t>
+          <t>134753</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26061</t>
+          <t>26224</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48708</t>
+          <t>47782</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4216,12 +4216,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126515</t>
+          <t>125983</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>174886</t>
+          <t>171596</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,66%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>971948</t>
+          <t>972687</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1022320</t>
+          <t>1021093</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>631939</t>
+          <t>635447</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>673583</t>
+          <t>674677</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,64%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1623261</t>
+          <t>1618579</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1684118</t>
+          <t>1682385</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134695</t>
+          <t>135922</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>185067</t>
+          <t>184328</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>91147</t>
+          <t>90053</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132791</t>
+          <t>129283</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>237627</t>
+          <t>239360</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>298484</t>
+          <t>303166</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,78%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>396120</t>
+          <t>394527</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>429749</t>
+          <t>430675</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,89%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>647947</t>
+          <t>647284</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>684006</t>
+          <t>685213</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1051752</t>
+          <t>1054849</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1101587</t>
+          <t>1106570</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,81%</t>
+          <t>83,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>87,13%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>78820</t>
+          <t>77894</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112449</t>
+          <t>114042</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>77516</t>
+          <t>76309</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>113575</t>
+          <t>114238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>168503</t>
+          <t>163520</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>218338</t>
+          <t>215241</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,95%</t>
         </is>
       </c>
     </row>
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>179795</t>
+          <t>180392</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>208641</t>
+          <t>208874</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,37%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>964800</t>
+          <t>965182</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1004937</t>
+          <t>1008647</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1153553</t>
+          <t>1154911</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1206366</t>
+          <t>1205463</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>83,96%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,8%</t>
+          <t>87,74%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58241</t>
+          <t>58008</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>87087</t>
+          <t>86490</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>102139</t>
+          <t>98429</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>142276</t>
+          <t>141894</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>167592</t>
+          <t>168495</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>220405</t>
+          <t>219047</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,94%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2806520</t>
+          <t>2806499</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2894389</t>
+          <t>2896366</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3066309</t>
+          <t>3069249</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3147187</t>
+          <t>3146952</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5902771</t>
+          <t>5898148</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6022539</t>
+          <t>6018559</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,48%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>522459</t>
+          <t>520482</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>610328</t>
+          <t>610349</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>395601</t>
+          <t>395836</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>476479</t>
+          <t>473539</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5593,7 +5593,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>937097</t>
+          <t>941077</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1056865</t>
+          <t>1061488</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -5807,7 +5807,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2016</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2016 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>337240</t>
+          <t>336518</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>369896</t>
+          <t>371431</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>281667</t>
+          <t>283644</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>308672</t>
+          <t>309512</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,16%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>630801</t>
+          <t>628317</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>672482</t>
+          <t>672111</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,6%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59196</t>
+          <t>57661</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91852</t>
+          <t>92574</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38383</t>
+          <t>37543</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65388</t>
+          <t>63411</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>103665</t>
+          <t>104036</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145346</t>
+          <t>147830</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,05%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>301580</t>
+          <t>300706</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>329274</t>
+          <t>329339</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>285467</t>
+          <t>284078</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>316804</t>
+          <t>315202</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>596227</t>
+          <t>596701</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>640040</t>
+          <t>638358</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>85,59%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>47055</t>
+          <t>46990</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>74749</t>
+          <t>75623</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52727</t>
+          <t>54329</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84064</t>
+          <t>85453</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>105820</t>
+          <t>107502</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149633</t>
+          <t>149159</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>389122</t>
+          <t>386505</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>427310</t>
+          <t>427344</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,96%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131234</t>
+          <t>130790</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149678</t>
+          <t>149190</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>89,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>526505</t>
+          <t>530002</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>570253</t>
+          <t>573518</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,7%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91797</t>
+          <t>91763</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129985</t>
+          <t>132602</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,04%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16445</t>
+          <t>16933</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34889</t>
+          <t>35333</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>114977</t>
+          <t>111712</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>158725</t>
+          <t>155228</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>895970</t>
+          <t>896621</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>954165</t>
+          <t>953096</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>624588</t>
+          <t>623170</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>672983</t>
+          <t>672926</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1536931</t>
+          <t>1537363</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1611309</t>
+          <t>1608757</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>81,56%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>193365</t>
+          <t>194434</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>251560</t>
+          <t>250909</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>151880</t>
+          <t>151937</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>200275</t>
+          <t>201693</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>361084</t>
+          <t>363636</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>435462</t>
+          <t>435030</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,06%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>474568</t>
+          <t>475249</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>516327</t>
+          <t>517672</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,46%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>608874</t>
+          <t>607839</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>646111</t>
+          <t>647272</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,6%</t>
+          <t>82,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1095825</t>
+          <t>1094502</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1152236</t>
+          <t>1152806</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,7%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,86%</t>
+          <t>84,9%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>104379</t>
+          <t>103034</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>146138</t>
+          <t>145457</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,54%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>91054</t>
+          <t>89893</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>128291</t>
+          <t>129326</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>205635</t>
+          <t>205065</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>262046</t>
+          <t>263369</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>185160</t>
+          <t>184095</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>216777</t>
+          <t>215336</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,75%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>895653</t>
+          <t>894510</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>943458</t>
+          <t>943959</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1094670</t>
+          <t>1094188</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1149620</t>
+          <t>1150013</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>84,09%</t>
+          <t>84,12%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>69381</t>
+          <t>70822</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>100998</t>
+          <t>102063</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>137571</t>
+          <t>137070</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>185376</t>
+          <t>186519</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>217567</t>
+          <t>217174</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>272517</t>
+          <t>272999</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,97%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2655876</t>
+          <t>2652640</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2752146</t>
+          <t>2748161</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2891807</t>
+          <t>2893553</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2983797</t>
+          <t>2982734</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,63%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5579892</t>
+          <t>5576578</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5708220</t>
+          <t>5710344</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,7%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>626776</t>
+          <t>630761</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>723046</t>
+          <t>726282</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>541969</t>
+          <t>543032</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>633959</t>
+          <t>632213</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1196468</t>
+          <t>1194344</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1324796</t>
+          <t>1328110</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,23%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B06_R-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36B06_R-Clase-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>361973</t>
+          <t>362281</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>396896</t>
+          <t>395894</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>245843</t>
+          <t>246242</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>271045</t>
+          <t>269684</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>617889</t>
+          <t>616896</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>660975</t>
+          <t>661969</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,82%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>76880</t>
+          <t>77882</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>111803</t>
+          <t>111495</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35635</t>
+          <t>36996</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60837</t>
+          <t>60438</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>119482</t>
+          <t>118488</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>162568</t>
+          <t>163561</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,96%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>271129</t>
+          <t>272054</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>303236</t>
+          <t>303409</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>272511</t>
+          <t>272258</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>305453</t>
+          <t>305029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,28%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>557075</t>
+          <t>555797</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>601383</t>
+          <t>599792</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,28%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>62816</t>
+          <t>62643</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94923</t>
+          <t>93998</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>66412</t>
+          <t>66836</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>99354</t>
+          <t>99607</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,72%</t>
+          <t>26,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>136534</t>
+          <t>138125</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180842</t>
+          <t>182120</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,68%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>394772</t>
+          <t>395067</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>435042</t>
+          <t>435002</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>124996</t>
+          <t>125323</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>146179</t>
+          <t>146625</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>527801</t>
+          <t>528325</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>573009</t>
+          <t>572686</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>80,69%</t>
+          <t>80,64%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107347</t>
+          <t>107387</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>147617</t>
+          <t>147322</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21603</t>
+          <t>21157</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42786</t>
+          <t>42459</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>137162</t>
+          <t>137485</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>182370</t>
+          <t>181846</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>924151</t>
+          <t>926886</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>987643</t>
+          <t>986797</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>559791</t>
+          <t>559128</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>602346</t>
+          <t>601901</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>78,37%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1499078</t>
+          <t>1499562</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1572838</t>
+          <t>1570343</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,81%</t>
+          <t>76,83%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,46%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>249743</t>
+          <t>250589</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>313235</t>
+          <t>310500</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111939</t>
+          <t>112384</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>154494</t>
+          <t>155157</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>378834</t>
+          <t>381329</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>452594</t>
+          <t>452110</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>228144</t>
+          <t>229113</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>263207</t>
+          <t>262964</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>434521</t>
+          <t>434676</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>472027</t>
+          <t>472441</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>76,54%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,15%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>676340</t>
+          <t>672910</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>726306</t>
+          <t>726506</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>79,12%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87348</t>
+          <t>87591</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>122411</t>
+          <t>121442</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>95665</t>
+          <t>95251</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>133171</t>
+          <t>133016</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>191941</t>
+          <t>191741</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>241907</t>
+          <t>245337</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>185821</t>
+          <t>186719</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>217930</t>
+          <t>218562</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1009531</t>
+          <t>1007345</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1062140</t>
+          <t>1058923</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>84,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1207097</t>
+          <t>1208521</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1269147</t>
+          <t>1267449</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,04%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>79228</t>
+          <t>78596</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>111337</t>
+          <t>110439</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>185644</t>
+          <t>188861</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>238253</t>
+          <t>240439</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>275795</t>
+          <t>277493</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>337845</t>
+          <t>336421</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,78%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2438510</t>
+          <t>2436486</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2540339</t>
+          <t>2537952</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2714021</t>
+          <t>2710333</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2798435</t>
+          <t>2798140</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5176475</t>
+          <t>5176711</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5309890</t>
+          <t>5309109</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,92%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>726979</t>
+          <t>729366</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>828808</t>
+          <t>830832</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>577654</t>
+          <t>577949</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>662068</t>
+          <t>665756</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1333516</t>
+          <t>1334297</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1466931</t>
+          <t>1466695</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3367,12 +3367,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>353163</t>
+          <t>351824</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>384995</t>
+          <t>383904</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3402,12 +3402,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>273669</t>
+          <t>273442</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>294744</t>
+          <t>295140</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3437,12 +3437,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>633947</t>
+          <t>632987</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>673299</t>
+          <t>672370</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3452,12 +3452,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -3480,12 +3480,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52216</t>
+          <t>53307</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>84048</t>
+          <t>85387</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3515,12 +3515,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18623</t>
+          <t>18227</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39698</t>
+          <t>39925</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3550,12 +3550,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>77278</t>
+          <t>78207</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>116630</t>
+          <t>117590</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3565,12 +3565,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>342684</t>
+          <t>341217</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>372129</t>
+          <t>372121</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -3745,12 +3745,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>279583</t>
+          <t>279972</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>304208</t>
+          <t>304983</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3760,12 +3760,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>630412</t>
+          <t>628812</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>669858</t>
+          <t>667601</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,57%</t>
         </is>
       </c>
     </row>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45627</t>
+          <t>45635</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75072</t>
+          <t>76539</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31757</t>
+          <t>30982</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>56382</t>
+          <t>55993</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3873,12 +3873,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>83863</t>
+          <t>86120</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>123309</t>
+          <t>124909</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3908,12 +3908,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,57%</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>494662</t>
+          <t>498141</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>536455</t>
+          <t>536563</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4068,12 +4068,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4088,12 +4088,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>212347</t>
+          <t>209973</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>233905</t>
+          <t>233916</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4103,7 +4103,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4123,12 +4123,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>717948</t>
+          <t>719166</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>763561</t>
+          <t>764076</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,9%</t>
         </is>
       </c>
     </row>
@@ -4166,12 +4166,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>92960</t>
+          <t>92852</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134753</t>
+          <t>131274</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4181,12 +4181,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4201,12 +4201,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>26224</t>
+          <t>26213</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47782</t>
+          <t>50156</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4236,12 +4236,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125983</t>
+          <t>125468</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>171596</t>
+          <t>170378</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,15%</t>
         </is>
       </c>
     </row>
@@ -4396,12 +4396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>972687</t>
+          <t>970893</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1021093</t>
+          <t>1019670</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4411,12 +4411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4431,12 +4431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>635447</t>
+          <t>634540</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>674677</t>
+          <t>674355</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4446,12 +4446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1618579</t>
+          <t>1617901</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1682385</t>
+          <t>1680224</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,43%</t>
         </is>
       </c>
     </row>
@@ -4509,12 +4509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135922</t>
+          <t>137345</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>184328</t>
+          <t>186122</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4524,12 +4524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4544,12 +4544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>90053</t>
+          <t>90375</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129283</t>
+          <t>130190</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4559,12 +4559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>239360</t>
+          <t>241521</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>303166</t>
+          <t>303844</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4594,12 +4594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -4739,12 +4739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>394527</t>
+          <t>394152</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>430675</t>
+          <t>429197</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4754,12 +4754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>647284</t>
+          <t>645953</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>685213</t>
+          <t>685517</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4789,12 +4789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1054849</t>
+          <t>1052325</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1106570</t>
+          <t>1103858</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>86,91%</t>
         </is>
       </c>
     </row>
@@ -4852,12 +4852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>77894</t>
+          <t>79372</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>114042</t>
+          <t>114417</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4867,12 +4867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4887,12 +4887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76309</t>
+          <t>76005</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>114238</t>
+          <t>115569</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4922,12 +4922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>163520</t>
+          <t>166232</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>215241</t>
+          <t>217765</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4937,12 +4937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>17,15%</t>
         </is>
       </c>
     </row>
@@ -5062,7 +5062,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>180392</t>
+          <t>180110</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>208874</t>
+          <t>208461</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>78,26%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5117,12 +5117,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>965182</t>
+          <t>961298</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1008647</t>
+          <t>1005098</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5152,12 +5152,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1154911</t>
+          <t>1154122</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1205463</t>
+          <t>1206977</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5167,12 +5167,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>87,74%</t>
+          <t>87,85%</t>
         </is>
       </c>
     </row>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>58008</t>
+          <t>58421</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>86490</t>
+          <t>86772</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5230,12 +5230,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>98429</t>
+          <t>101978</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>141894</t>
+          <t>145778</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5265,12 +5265,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>168495</t>
+          <t>166981</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>219047</t>
+          <t>219836</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,0%</t>
         </is>
       </c>
     </row>
@@ -5425,12 +5425,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2806499</t>
+          <t>2804895</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2896366</t>
+          <t>2895501</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5440,12 +5440,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>82,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3069249</t>
+          <t>3066359</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3146952</t>
+          <t>3148196</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5475,12 +5475,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5495,12 +5495,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5898148</t>
+          <t>5894273</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6018559</t>
+          <t>6015919</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5510,12 +5510,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,44%</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>520482</t>
+          <t>521347</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>610349</t>
+          <t>611953</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5553,12 +5553,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>15,26%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5573,12 +5573,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>395836</t>
+          <t>394592</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>473539</t>
+          <t>476429</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5588,12 +5588,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5608,12 +5608,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>941077</t>
+          <t>943717</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1061488</t>
+          <t>1065363</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5623,12 +5623,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -6002,12 +6002,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>336518</t>
+          <t>338110</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>371431</t>
+          <t>370787</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>283644</t>
+          <t>282875</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>309512</t>
+          <t>309158</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6072,12 +6072,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>628317</t>
+          <t>626664</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>672111</t>
+          <t>673363</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6087,12 +6087,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,76%</t>
         </is>
       </c>
     </row>
@@ -6115,12 +6115,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57661</t>
+          <t>58305</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92574</t>
+          <t>90982</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>37543</t>
+          <t>37897</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63411</t>
+          <t>64180</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6185,12 +6185,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>104036</t>
+          <t>102784</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>147830</t>
+          <t>149483</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6200,12 +6200,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,26%</t>
         </is>
       </c>
     </row>
@@ -6345,12 +6345,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>300706</t>
+          <t>300580</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>329339</t>
+          <t>329751</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6380,12 +6380,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>284078</t>
+          <t>284250</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>315202</t>
+          <t>315489</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6415,12 +6415,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>596701</t>
+          <t>598153</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>638358</t>
+          <t>638698</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,63%</t>
         </is>
       </c>
     </row>
@@ -6458,12 +6458,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>46990</t>
+          <t>46578</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>75623</t>
+          <t>75749</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6493,12 +6493,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>54329</t>
+          <t>54042</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>85453</t>
+          <t>85281</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6528,12 +6528,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>107502</t>
+          <t>107162</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149159</t>
+          <t>147707</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6543,12 +6543,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -6688,12 +6688,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>386505</t>
+          <t>389565</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>427344</t>
+          <t>427703</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>82,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6723,12 +6723,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>130790</t>
+          <t>129432</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149190</t>
+          <t>148991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6758,12 +6758,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>530002</t>
+          <t>528376</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>573518</t>
+          <t>570769</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6773,12 +6773,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,3%</t>
         </is>
       </c>
     </row>
@@ -6801,12 +6801,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91763</t>
+          <t>91404</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>132602</t>
+          <t>129542</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6836,12 +6836,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16933</t>
+          <t>17132</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35333</t>
+          <t>36691</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6871,12 +6871,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>111712</t>
+          <t>114461</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>155228</t>
+          <t>156854</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,89%</t>
         </is>
       </c>
     </row>
@@ -7031,12 +7031,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>896621</t>
+          <t>893906</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>953096</t>
+          <t>949839</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,06%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>623170</t>
+          <t>623753</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>672926</t>
+          <t>670545</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,55%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7101,12 +7101,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1537363</t>
+          <t>1535812</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1608757</t>
+          <t>1608234</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>81,54%</t>
         </is>
       </c>
     </row>
@@ -7144,12 +7144,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>194434</t>
+          <t>197691</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>250909</t>
+          <t>253624</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7179,12 +7179,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>151937</t>
+          <t>154318</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>201693</t>
+          <t>201110</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7214,12 +7214,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>363636</t>
+          <t>364159</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>435030</t>
+          <t>436581</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7229,12 +7229,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,13%</t>
         </is>
       </c>
     </row>
@@ -7374,12 +7374,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>475249</t>
+          <t>475533</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>517672</t>
+          <t>516401</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7409,12 +7409,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>607839</t>
+          <t>608256</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>647272</t>
+          <t>648207</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,46%</t>
+          <t>82,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1094502</t>
+          <t>1097170</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1152806</t>
+          <t>1154723</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>85,04%</t>
         </is>
       </c>
     </row>
@@ -7487,12 +7487,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103034</t>
+          <t>104305</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>145457</t>
+          <t>145173</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7522,12 +7522,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89893</t>
+          <t>88958</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>129326</t>
+          <t>128909</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,54%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>205065</t>
+          <t>203148</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>263369</t>
+          <t>260701</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,2%</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7697,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>184095</t>
+          <t>183883</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>215336</t>
+          <t>214972</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,25%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>894510</t>
+          <t>896246</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>943959</t>
+          <t>943884</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>82,75%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1094188</t>
+          <t>1093792</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1150013</t>
+          <t>1149321</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7802,12 +7802,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,06%</t>
         </is>
       </c>
     </row>
@@ -7830,12 +7830,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70822</t>
+          <t>71186</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102063</t>
+          <t>102275</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>137070</t>
+          <t>137145</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>186519</t>
+          <t>184783</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7900,12 +7900,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>217174</t>
+          <t>217866</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>272999</t>
+          <t>273395</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,0%</t>
         </is>
       </c>
     </row>
@@ -8060,12 +8060,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2652640</t>
+          <t>2659933</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>2748161</t>
+          <t>2749604</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,51%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,33%</t>
+          <t>81,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2893553</t>
+          <t>2883915</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2982734</t>
+          <t>2983030</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8130,12 +8130,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5576578</t>
+          <t>5572924</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>5710344</t>
+          <t>5706778</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,7%</t>
+          <t>82,65%</t>
         </is>
       </c>
     </row>
@@ -8173,12 +8173,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>630761</t>
+          <t>629318</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>726282</t>
+          <t>718989</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>18,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>543032</t>
+          <t>542736</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>632213</t>
+          <t>641851</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1194344</t>
+          <t>1197910</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1328110</t>
+          <t>1331764</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
